--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117502836</v>
+        <v>117502835</v>
       </c>
       <c r="B4" t="n">
-        <v>56695</v>
+        <v>56718</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,20 +940,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102952</v>
+        <v>100091</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117502826</v>
+        <v>117502836</v>
       </c>
       <c r="B5" t="n">
-        <v>56398</v>
+        <v>56695</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,26 +1068,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102932</v>
+        <v>102952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117502835</v>
+        <v>117502826</v>
       </c>
       <c r="B6" t="n">
-        <v>56718</v>
+        <v>56398</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,30 +1188,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100091</v>
+        <v>102932</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117502835</v>
+        <v>117502826</v>
       </c>
       <c r="B4" t="n">
-        <v>56718</v>
+        <v>56399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,30 +940,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100091</v>
+        <v>102932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
         <v>117502836</v>
       </c>
       <c r="B5" t="n">
-        <v>56695</v>
+        <v>56696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117502826</v>
+        <v>117502835</v>
       </c>
       <c r="B6" t="n">
-        <v>56398</v>
+        <v>56719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,30 +1188,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>100091</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,6 +1298,130 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125881695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57499</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102117</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jorduggla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Asio flammeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röjnäset Gärdefjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>804463</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7155014</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Landade på staketstolpe intill betande kor. Sitter och spanar ända tills vi lämnar området.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Uno Skog, Grim Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>125881695</v>
       </c>
       <c r="B7" t="n">
-        <v>57499</v>
+        <v>57500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>125881695</v>
       </c>
       <c r="B7" t="n">
-        <v>57500</v>
+        <v>57504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63593-2019 artfynd.xlsx
+++ b/artfynd/A 63593-2019 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>125881695</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>57505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
